--- a/App files/TEMPLATES/PSRV Format.xlsx
+++ b/App files/TEMPLATES/PSRV Format.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\PSRV AUTOMATION\TEMPLATES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\775491\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71DAA0A-1A24-405B-96B5-4B53163F4CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF887BBB-F680-4F34-ADA0-E09EFD2644FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4935" yWindow="15" windowWidth="19170" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSRV Formet" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -592,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -819,6 +821,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -867,15 +887,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,6 +929,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -924,20 +941,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,15 +964,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,6 +980,71 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>452437</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>107155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>250030</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Oval 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF9BDED-8AF3-3DD0-AEA7-1D2173CF6A4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9691687" y="3476624"/>
+          <a:ext cx="119063" cy="142875"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1549,83 +1613,83 @@
       <c r="AK6" s="87"/>
     </row>
     <row r="7" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="89"/>
-      <c r="K7" s="89"/>
-      <c r="L7" s="90"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="96"/>
       <c r="M7" s="14"/>
-      <c r="Y7" s="94" t="s">
+      <c r="Y7" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="Z7" s="94"/>
-      <c r="AA7" s="94"/>
-      <c r="AB7" s="94"/>
-      <c r="AC7" s="94"/>
-      <c r="AD7" s="134"/>
-      <c r="AE7" s="135"/>
-      <c r="AF7" s="135"/>
-      <c r="AG7" s="135"/>
-      <c r="AH7" s="135"/>
-      <c r="AI7" s="135"/>
-      <c r="AJ7" s="135"/>
-      <c r="AK7" s="136"/>
+      <c r="Z7" s="100"/>
+      <c r="AA7" s="100"/>
+      <c r="AB7" s="100"/>
+      <c r="AC7" s="100"/>
+      <c r="AD7" s="128"/>
+      <c r="AE7" s="128"/>
+      <c r="AF7" s="128"/>
+      <c r="AG7" s="128"/>
+      <c r="AH7" s="128"/>
+      <c r="AI7" s="128"/>
+      <c r="AJ7" s="128"/>
+      <c r="AK7" s="129"/>
     </row>
     <row r="8" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="95"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
-      <c r="S8" s="92"/>
-      <c r="T8" s="92"/>
-      <c r="U8" s="92"/>
-      <c r="V8" s="92"/>
-      <c r="W8" s="92"/>
-      <c r="X8" s="92"/>
-      <c r="Y8" s="92"/>
-      <c r="Z8" s="92"/>
-      <c r="AA8" s="92"/>
-      <c r="AB8" s="92"/>
-      <c r="AC8" s="92"/>
-      <c r="AD8" s="92"/>
+      <c r="A8" s="97"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
       <c r="AE8" s="80"/>
-      <c r="AF8" s="92"/>
-      <c r="AG8" s="92"/>
-      <c r="AH8" s="92"/>
-      <c r="AI8" s="92"/>
-      <c r="AJ8" s="93"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="99"/>
       <c r="AK8" s="45"/>
     </row>
     <row r="9" spans="1:37" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
       <c r="G9" s="74"/>
       <c r="H9" s="74"/>
       <c r="I9" s="74"/>
@@ -1641,19 +1705,19 @@
       <c r="S9" s="74"/>
       <c r="T9" s="74"/>
       <c r="U9" s="74"/>
-      <c r="V9" s="96" t="s">
+      <c r="V9" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="W9" s="97"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="97"/>
-      <c r="Z9" s="97"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="103"/>
+      <c r="Z9" s="103"/>
       <c r="AA9" s="18"/>
-      <c r="AB9" s="107" t="s">
+      <c r="AB9" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="AC9" s="107"/>
-      <c r="AD9" s="107"/>
+      <c r="AC9" s="111"/>
+      <c r="AD9" s="111"/>
       <c r="AE9" s="30"/>
       <c r="AF9" s="18"/>
       <c r="AG9" s="4" t="s">
@@ -1665,59 +1729,59 @@
       <c r="AK9" s="46"/>
     </row>
     <row r="10" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="102"/>
-      <c r="U10" s="103"/>
-      <c r="V10" s="96" t="s">
+      <c r="B10" s="107"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="108"/>
+      <c r="Q10" s="108"/>
+      <c r="R10" s="108"/>
+      <c r="S10" s="108"/>
+      <c r="T10" s="108"/>
+      <c r="U10" s="109"/>
+      <c r="V10" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="W10" s="97"/>
-      <c r="X10" s="97"/>
-      <c r="Y10" s="97"/>
-      <c r="Z10" s="97"/>
-      <c r="AA10" s="97"/>
-      <c r="AB10" s="97"/>
-      <c r="AC10" s="97"/>
-      <c r="AD10" s="97"/>
-      <c r="AE10" s="98"/>
-      <c r="AF10" s="97"/>
-      <c r="AG10" s="97"/>
-      <c r="AH10" s="97"/>
-      <c r="AI10" s="97"/>
-      <c r="AJ10" s="99"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
+      <c r="Y10" s="103"/>
+      <c r="Z10" s="103"/>
+      <c r="AA10" s="103"/>
+      <c r="AB10" s="103"/>
+      <c r="AC10" s="103"/>
+      <c r="AD10" s="103"/>
+      <c r="AE10" s="104"/>
+      <c r="AF10" s="103"/>
+      <c r="AG10" s="103"/>
+      <c r="AH10" s="103"/>
+      <c r="AI10" s="103"/>
+      <c r="AJ10" s="105"/>
       <c r="AK10" s="46"/>
     </row>
     <row r="11" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
       <c r="I11" s="20" t="s">
         <v>18</v>
       </c>
@@ -1726,8 +1790,8 @@
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
+      <c r="O11" s="124"/>
+      <c r="P11" s="124"/>
       <c r="Q11" s="20" t="s">
         <v>19</v>
       </c>
@@ -1735,16 +1799,16 @@
       <c r="S11" s="23"/>
       <c r="T11" s="23"/>
       <c r="U11" s="24"/>
-      <c r="V11" s="107"/>
-      <c r="W11" s="107"/>
+      <c r="V11" s="111"/>
+      <c r="W11" s="111"/>
       <c r="X11" s="6" t="s">
         <v>20</v>
       </c>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
-      <c r="AB11" s="107"/>
-      <c r="AC11" s="107"/>
+      <c r="AB11" s="111"/>
+      <c r="AC11" s="111"/>
       <c r="AD11" s="6" t="s">
         <v>21</v>
       </c>
@@ -1780,36 +1844,36 @@
       <c r="S12" s="4"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
-      <c r="V12" s="96" t="s">
+      <c r="V12" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="W12" s="97"/>
-      <c r="X12" s="97"/>
-      <c r="Y12" s="97"/>
-      <c r="Z12" s="99"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="103"/>
+      <c r="Y12" s="103"/>
+      <c r="Z12" s="105"/>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="8"/>
-      <c r="AG12" s="133" t="s">
+      <c r="AG12" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="AH12" s="133"/>
-      <c r="AI12" s="133"/>
+      <c r="AH12" s="135"/>
+      <c r="AI12" s="135"/>
       <c r="AJ12" s="43"/>
       <c r="AK12" s="46"/>
     </row>
     <row r="13" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
@@ -1832,21 +1896,21 @@
       <c r="X13" s="29"/>
       <c r="Y13" s="29"/>
       <c r="Z13" s="7"/>
-      <c r="AA13" s="104" t="s">
+      <c r="AA13" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="AB13" s="105"/>
-      <c r="AC13" s="106"/>
+      <c r="AB13" s="110"/>
+      <c r="AC13" s="93"/>
       <c r="AD13" s="7"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="26"/>
-      <c r="AG13" s="128" t="s">
+      <c r="AG13" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="AH13" s="129"/>
-      <c r="AI13" s="129"/>
-      <c r="AJ13" s="129"/>
-      <c r="AK13" s="130"/>
+      <c r="AH13" s="131"/>
+      <c r="AI13" s="131"/>
+      <c r="AJ13" s="131"/>
+      <c r="AK13" s="132"/>
     </row>
     <row r="14" spans="1:37" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="47"/>
@@ -1891,52 +1955,52 @@
       <c r="A15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="108" t="s">
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="109"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="109"/>
-      <c r="R15" s="109"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="111" t="s">
+      <c r="N15" s="113"/>
+      <c r="O15" s="113"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="113"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="U15" s="112"/>
-      <c r="V15" s="124" t="s">
+      <c r="U15" s="116"/>
+      <c r="V15" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="W15" s="124"/>
-      <c r="X15" s="124"/>
-      <c r="Y15" s="124" t="s">
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="Z15" s="124"/>
-      <c r="AA15" s="124" t="s">
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="AB15" s="124"/>
-      <c r="AC15" s="124"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
       <c r="AD15" s="50"/>
-      <c r="AE15" s="107" t="s">
+      <c r="AE15" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="AF15" s="107"/>
-      <c r="AG15" s="107"/>
+      <c r="AF15" s="111"/>
+      <c r="AG15" s="111"/>
       <c r="AH15" s="19"/>
       <c r="AI15" s="31" t="s">
         <v>29</v>
@@ -1963,70 +2027,70 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="114"/>
-      <c r="R16" s="114"/>
-      <c r="S16" s="115"/>
-      <c r="T16" s="104"/>
-      <c r="U16" s="106"/>
-      <c r="V16" s="125"/>
-      <c r="W16" s="126"/>
-      <c r="X16" s="127"/>
-      <c r="Y16" s="104"/>
-      <c r="Z16" s="106"/>
-      <c r="AA16" s="104"/>
-      <c r="AB16" s="105"/>
-      <c r="AC16" s="106"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="92"/>
+      <c r="U16" s="93"/>
+      <c r="V16" s="89"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="91"/>
+      <c r="Y16" s="92"/>
+      <c r="Z16" s="93"/>
+      <c r="AA16" s="92"/>
+      <c r="AB16" s="110"/>
+      <c r="AC16" s="93"/>
       <c r="AD16" s="38"/>
-      <c r="AE16" s="124"/>
-      <c r="AF16" s="124"/>
-      <c r="AG16" s="124"/>
+      <c r="AE16" s="88"/>
+      <c r="AF16" s="88"/>
+      <c r="AG16" s="88"/>
       <c r="AH16" s="15"/>
       <c r="AI16" s="4"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="53"/>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="120"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="121"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="121"/>
-      <c r="S17" s="121"/>
-      <c r="T17" s="121"/>
-      <c r="U17" s="121"/>
-      <c r="V17" s="121"/>
-      <c r="W17" s="121"/>
-      <c r="X17" s="121"/>
-      <c r="Y17" s="121"/>
-      <c r="Z17" s="121"/>
-      <c r="AA17" s="121"/>
-      <c r="AB17" s="121"/>
-      <c r="AC17" s="121"/>
-      <c r="AD17" s="121"/>
-      <c r="AE17" s="121"/>
-      <c r="AF17" s="121"/>
-      <c r="AG17" s="121"/>
-      <c r="AH17" s="121"/>
-      <c r="AI17" s="121"/>
-      <c r="AJ17" s="121"/>
-      <c r="AK17" s="122"/>
+      <c r="A17" s="125"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="126"/>
+      <c r="U17" s="126"/>
+      <c r="V17" s="126"/>
+      <c r="W17" s="126"/>
+      <c r="X17" s="126"/>
+      <c r="Y17" s="126"/>
+      <c r="Z17" s="126"/>
+      <c r="AA17" s="126"/>
+      <c r="AB17" s="126"/>
+      <c r="AC17" s="126"/>
+      <c r="AD17" s="126"/>
+      <c r="AE17" s="126"/>
+      <c r="AF17" s="126"/>
+      <c r="AG17" s="126"/>
+      <c r="AH17" s="126"/>
+      <c r="AI17" s="126"/>
+      <c r="AJ17" s="126"/>
+      <c r="AK17" s="127"/>
     </row>
     <row r="18" spans="1:37" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52">
@@ -2043,70 +2107,70 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="105"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
-      <c r="Q18" s="105"/>
-      <c r="R18" s="105"/>
-      <c r="S18" s="106"/>
-      <c r="T18" s="104"/>
-      <c r="U18" s="106"/>
-      <c r="V18" s="104"/>
-      <c r="W18" s="105"/>
-      <c r="X18" s="106"/>
-      <c r="Y18" s="104"/>
-      <c r="Z18" s="106"/>
-      <c r="AA18" s="107"/>
-      <c r="AB18" s="107"/>
-      <c r="AC18" s="107"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="110"/>
+      <c r="S18" s="93"/>
+      <c r="T18" s="92"/>
+      <c r="U18" s="93"/>
+      <c r="V18" s="92"/>
+      <c r="W18" s="110"/>
+      <c r="X18" s="93"/>
+      <c r="Y18" s="92"/>
+      <c r="Z18" s="93"/>
+      <c r="AA18" s="111"/>
+      <c r="AB18" s="111"/>
+      <c r="AC18" s="111"/>
       <c r="AD18" s="39"/>
-      <c r="AE18" s="107"/>
-      <c r="AF18" s="107"/>
-      <c r="AG18" s="107"/>
+      <c r="AE18" s="111"/>
+      <c r="AF18" s="111"/>
+      <c r="AG18" s="111"/>
       <c r="AH18" s="15"/>
       <c r="AI18" s="4"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="53"/>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="120"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="121"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="121"/>
-      <c r="S19" s="121"/>
-      <c r="T19" s="121"/>
-      <c r="U19" s="121"/>
-      <c r="V19" s="121"/>
-      <c r="W19" s="121"/>
-      <c r="X19" s="121"/>
-      <c r="Y19" s="121"/>
-      <c r="Z19" s="121"/>
-      <c r="AA19" s="121"/>
-      <c r="AB19" s="121"/>
-      <c r="AC19" s="121"/>
-      <c r="AD19" s="121"/>
-      <c r="AE19" s="121"/>
-      <c r="AF19" s="121"/>
-      <c r="AG19" s="121"/>
-      <c r="AH19" s="121"/>
-      <c r="AI19" s="121"/>
-      <c r="AJ19" s="121"/>
-      <c r="AK19" s="122"/>
+      <c r="A19" s="125"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="126"/>
+      <c r="U19" s="126"/>
+      <c r="V19" s="126"/>
+      <c r="W19" s="126"/>
+      <c r="X19" s="126"/>
+      <c r="Y19" s="126"/>
+      <c r="Z19" s="126"/>
+      <c r="AA19" s="126"/>
+      <c r="AB19" s="126"/>
+      <c r="AC19" s="126"/>
+      <c r="AD19" s="126"/>
+      <c r="AE19" s="126"/>
+      <c r="AF19" s="126"/>
+      <c r="AG19" s="126"/>
+      <c r="AH19" s="126"/>
+      <c r="AI19" s="126"/>
+      <c r="AJ19" s="126"/>
+      <c r="AK19" s="127"/>
     </row>
     <row r="20" spans="1:37" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52">
@@ -2123,70 +2187,70 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="106"/>
-      <c r="T20" s="104"/>
-      <c r="U20" s="106"/>
-      <c r="V20" s="104"/>
-      <c r="W20" s="105"/>
-      <c r="X20" s="106"/>
-      <c r="Y20" s="104"/>
-      <c r="Z20" s="106"/>
-      <c r="AA20" s="107"/>
-      <c r="AB20" s="107"/>
-      <c r="AC20" s="107"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="110"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="93"/>
+      <c r="T20" s="92"/>
+      <c r="U20" s="93"/>
+      <c r="V20" s="92"/>
+      <c r="W20" s="110"/>
+      <c r="X20" s="93"/>
+      <c r="Y20" s="92"/>
+      <c r="Z20" s="93"/>
+      <c r="AA20" s="111"/>
+      <c r="AB20" s="111"/>
+      <c r="AC20" s="111"/>
       <c r="AD20" s="35"/>
-      <c r="AE20" s="107"/>
-      <c r="AF20" s="107"/>
-      <c r="AG20" s="107"/>
+      <c r="AE20" s="111"/>
+      <c r="AF20" s="111"/>
+      <c r="AG20" s="111"/>
       <c r="AH20" s="15"/>
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="53"/>
     </row>
     <row r="21" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="120"/>
-      <c r="B21" s="121"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="121"/>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="121"/>
-      <c r="S21" s="121"/>
-      <c r="T21" s="121"/>
-      <c r="U21" s="121"/>
-      <c r="V21" s="121"/>
-      <c r="W21" s="121"/>
-      <c r="X21" s="121"/>
-      <c r="Y21" s="121"/>
-      <c r="Z21" s="121"/>
-      <c r="AA21" s="121"/>
-      <c r="AB21" s="121"/>
-      <c r="AC21" s="121"/>
-      <c r="AD21" s="121"/>
-      <c r="AE21" s="121"/>
-      <c r="AF21" s="121"/>
-      <c r="AG21" s="121"/>
-      <c r="AH21" s="121"/>
-      <c r="AI21" s="121"/>
-      <c r="AJ21" s="121"/>
-      <c r="AK21" s="122"/>
+      <c r="A21" s="125"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="126"/>
+      <c r="S21" s="126"/>
+      <c r="T21" s="126"/>
+      <c r="U21" s="126"/>
+      <c r="V21" s="126"/>
+      <c r="W21" s="126"/>
+      <c r="X21" s="126"/>
+      <c r="Y21" s="126"/>
+      <c r="Z21" s="126"/>
+      <c r="AA21" s="126"/>
+      <c r="AB21" s="126"/>
+      <c r="AC21" s="126"/>
+      <c r="AD21" s="126"/>
+      <c r="AE21" s="126"/>
+      <c r="AF21" s="126"/>
+      <c r="AG21" s="126"/>
+      <c r="AH21" s="126"/>
+      <c r="AI21" s="126"/>
+      <c r="AJ21" s="126"/>
+      <c r="AK21" s="127"/>
     </row>
     <row r="22" spans="1:37" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="52">
@@ -2203,70 +2267,70 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="105"/>
-      <c r="Q22" s="105"/>
-      <c r="R22" s="105"/>
-      <c r="S22" s="106"/>
-      <c r="T22" s="104"/>
-      <c r="U22" s="106"/>
-      <c r="V22" s="104"/>
-      <c r="W22" s="105"/>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="104"/>
-      <c r="Z22" s="106"/>
-      <c r="AA22" s="107"/>
-      <c r="AB22" s="107"/>
-      <c r="AC22" s="107"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="110"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="110"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="92"/>
+      <c r="U22" s="93"/>
+      <c r="V22" s="92"/>
+      <c r="W22" s="110"/>
+      <c r="X22" s="93"/>
+      <c r="Y22" s="92"/>
+      <c r="Z22" s="93"/>
+      <c r="AA22" s="111"/>
+      <c r="AB22" s="111"/>
+      <c r="AC22" s="111"/>
       <c r="AD22" s="39"/>
-      <c r="AE22" s="104"/>
-      <c r="AF22" s="105"/>
-      <c r="AG22" s="106"/>
+      <c r="AE22" s="92"/>
+      <c r="AF22" s="110"/>
+      <c r="AG22" s="93"/>
       <c r="AH22" s="15"/>
       <c r="AI22" s="4"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="53"/>
     </row>
     <row r="23" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="120"/>
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="121"/>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="121"/>
-      <c r="S23" s="121"/>
-      <c r="T23" s="121"/>
-      <c r="U23" s="121"/>
-      <c r="V23" s="121"/>
-      <c r="W23" s="121"/>
-      <c r="X23" s="121"/>
-      <c r="Y23" s="121"/>
-      <c r="Z23" s="121"/>
-      <c r="AA23" s="121"/>
-      <c r="AB23" s="121"/>
-      <c r="AC23" s="121"/>
-      <c r="AD23" s="121"/>
-      <c r="AE23" s="121"/>
-      <c r="AF23" s="121"/>
-      <c r="AG23" s="121"/>
-      <c r="AH23" s="121"/>
-      <c r="AI23" s="121"/>
-      <c r="AJ23" s="121"/>
-      <c r="AK23" s="122"/>
+      <c r="A23" s="125"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="126"/>
+      <c r="O23" s="126"/>
+      <c r="P23" s="126"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="126"/>
+      <c r="S23" s="126"/>
+      <c r="T23" s="126"/>
+      <c r="U23" s="126"/>
+      <c r="V23" s="126"/>
+      <c r="W23" s="126"/>
+      <c r="X23" s="126"/>
+      <c r="Y23" s="126"/>
+      <c r="Z23" s="126"/>
+      <c r="AA23" s="126"/>
+      <c r="AB23" s="126"/>
+      <c r="AC23" s="126"/>
+      <c r="AD23" s="126"/>
+      <c r="AE23" s="126"/>
+      <c r="AF23" s="126"/>
+      <c r="AG23" s="126"/>
+      <c r="AH23" s="126"/>
+      <c r="AI23" s="126"/>
+      <c r="AJ23" s="126"/>
+      <c r="AK23" s="127"/>
     </row>
     <row r="24" spans="1:37" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="52">
@@ -2283,70 +2347,70 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="105"/>
-      <c r="Q24" s="105"/>
-      <c r="R24" s="105"/>
-      <c r="S24" s="106"/>
-      <c r="T24" s="104"/>
-      <c r="U24" s="106"/>
-      <c r="V24" s="104"/>
-      <c r="W24" s="105"/>
-      <c r="X24" s="106"/>
-      <c r="Y24" s="104"/>
-      <c r="Z24" s="106"/>
-      <c r="AA24" s="107"/>
-      <c r="AB24" s="107"/>
-      <c r="AC24" s="107"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="110"/>
+      <c r="O24" s="110"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="110"/>
+      <c r="R24" s="110"/>
+      <c r="S24" s="93"/>
+      <c r="T24" s="92"/>
+      <c r="U24" s="93"/>
+      <c r="V24" s="92"/>
+      <c r="W24" s="110"/>
+      <c r="X24" s="93"/>
+      <c r="Y24" s="92"/>
+      <c r="Z24" s="93"/>
+      <c r="AA24" s="111"/>
+      <c r="AB24" s="111"/>
+      <c r="AC24" s="111"/>
       <c r="AD24" s="39"/>
-      <c r="AE24" s="104"/>
-      <c r="AF24" s="105"/>
-      <c r="AG24" s="106"/>
+      <c r="AE24" s="92"/>
+      <c r="AF24" s="110"/>
+      <c r="AG24" s="93"/>
       <c r="AH24" s="15"/>
       <c r="AI24" s="4"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="53"/>
     </row>
     <row r="25" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="120"/>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="121"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="121"/>
-      <c r="N25" s="121"/>
-      <c r="O25" s="121"/>
-      <c r="P25" s="121"/>
-      <c r="Q25" s="121"/>
-      <c r="R25" s="121"/>
-      <c r="S25" s="121"/>
-      <c r="T25" s="121"/>
-      <c r="U25" s="121"/>
-      <c r="V25" s="121"/>
-      <c r="W25" s="121"/>
-      <c r="X25" s="121"/>
-      <c r="Y25" s="121"/>
-      <c r="Z25" s="121"/>
-      <c r="AA25" s="121"/>
-      <c r="AB25" s="121"/>
-      <c r="AC25" s="121"/>
-      <c r="AD25" s="121"/>
-      <c r="AE25" s="121"/>
-      <c r="AF25" s="121"/>
-      <c r="AG25" s="121"/>
-      <c r="AH25" s="121"/>
-      <c r="AI25" s="121"/>
-      <c r="AJ25" s="121"/>
-      <c r="AK25" s="122"/>
+      <c r="A25" s="125"/>
+      <c r="B25" s="126"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="126"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="126"/>
+      <c r="N25" s="126"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="126"/>
+      <c r="S25" s="126"/>
+      <c r="T25" s="126"/>
+      <c r="U25" s="126"/>
+      <c r="V25" s="126"/>
+      <c r="W25" s="126"/>
+      <c r="X25" s="126"/>
+      <c r="Y25" s="126"/>
+      <c r="Z25" s="126"/>
+      <c r="AA25" s="126"/>
+      <c r="AB25" s="126"/>
+      <c r="AC25" s="126"/>
+      <c r="AD25" s="126"/>
+      <c r="AE25" s="126"/>
+      <c r="AF25" s="126"/>
+      <c r="AG25" s="126"/>
+      <c r="AH25" s="126"/>
+      <c r="AI25" s="126"/>
+      <c r="AJ25" s="126"/>
+      <c r="AK25" s="127"/>
     </row>
     <row r="26" spans="1:37" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="52">
@@ -2363,70 +2427,70 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="105"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="105"/>
-      <c r="Q26" s="105"/>
-      <c r="R26" s="105"/>
-      <c r="S26" s="106"/>
-      <c r="T26" s="104"/>
-      <c r="U26" s="106"/>
-      <c r="V26" s="104"/>
-      <c r="W26" s="105"/>
-      <c r="X26" s="106"/>
-      <c r="Y26" s="104"/>
-      <c r="Z26" s="106"/>
-      <c r="AA26" s="107"/>
-      <c r="AB26" s="107"/>
-      <c r="AC26" s="107"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="110"/>
+      <c r="O26" s="110"/>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="110"/>
+      <c r="R26" s="110"/>
+      <c r="S26" s="93"/>
+      <c r="T26" s="92"/>
+      <c r="U26" s="93"/>
+      <c r="V26" s="92"/>
+      <c r="W26" s="110"/>
+      <c r="X26" s="93"/>
+      <c r="Y26" s="92"/>
+      <c r="Z26" s="93"/>
+      <c r="AA26" s="111"/>
+      <c r="AB26" s="111"/>
+      <c r="AC26" s="111"/>
       <c r="AD26" s="39"/>
-      <c r="AE26" s="104"/>
-      <c r="AF26" s="105"/>
-      <c r="AG26" s="106"/>
+      <c r="AE26" s="92"/>
+      <c r="AF26" s="110"/>
+      <c r="AG26" s="93"/>
       <c r="AH26" s="15"/>
       <c r="AI26" s="4"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="53"/>
     </row>
     <row r="27" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="120"/>
-      <c r="B27" s="121"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="121"/>
-      <c r="H27" s="121"/>
-      <c r="I27" s="121"/>
-      <c r="J27" s="121"/>
-      <c r="K27" s="121"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="121"/>
-      <c r="N27" s="121"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="121"/>
-      <c r="Q27" s="121"/>
-      <c r="R27" s="121"/>
-      <c r="S27" s="121"/>
-      <c r="T27" s="121"/>
-      <c r="U27" s="121"/>
-      <c r="V27" s="121"/>
-      <c r="W27" s="121"/>
-      <c r="X27" s="121"/>
-      <c r="Y27" s="121"/>
-      <c r="Z27" s="121"/>
-      <c r="AA27" s="121"/>
-      <c r="AB27" s="121"/>
-      <c r="AC27" s="121"/>
-      <c r="AD27" s="121"/>
-      <c r="AE27" s="121"/>
-      <c r="AF27" s="121"/>
-      <c r="AG27" s="121"/>
-      <c r="AH27" s="121"/>
-      <c r="AI27" s="121"/>
-      <c r="AJ27" s="121"/>
-      <c r="AK27" s="122"/>
+      <c r="A27" s="125"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="126"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="126"/>
+      <c r="N27" s="126"/>
+      <c r="O27" s="126"/>
+      <c r="P27" s="126"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="126"/>
+      <c r="S27" s="126"/>
+      <c r="T27" s="126"/>
+      <c r="U27" s="126"/>
+      <c r="V27" s="126"/>
+      <c r="W27" s="126"/>
+      <c r="X27" s="126"/>
+      <c r="Y27" s="126"/>
+      <c r="Z27" s="126"/>
+      <c r="AA27" s="126"/>
+      <c r="AB27" s="126"/>
+      <c r="AC27" s="126"/>
+      <c r="AD27" s="126"/>
+      <c r="AE27" s="126"/>
+      <c r="AF27" s="126"/>
+      <c r="AG27" s="126"/>
+      <c r="AH27" s="126"/>
+      <c r="AI27" s="126"/>
+      <c r="AJ27" s="126"/>
+      <c r="AK27" s="127"/>
     </row>
     <row r="28" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="52">
@@ -2443,27 +2507,27 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="105"/>
-      <c r="O28" s="105"/>
-      <c r="P28" s="105"/>
-      <c r="Q28" s="105"/>
-      <c r="R28" s="105"/>
-      <c r="S28" s="106"/>
-      <c r="T28" s="104"/>
-      <c r="U28" s="106"/>
-      <c r="V28" s="104"/>
-      <c r="W28" s="105"/>
-      <c r="X28" s="106"/>
-      <c r="Y28" s="104"/>
-      <c r="Z28" s="106"/>
-      <c r="AA28" s="107"/>
-      <c r="AB28" s="107"/>
-      <c r="AC28" s="107"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="110"/>
+      <c r="O28" s="110"/>
+      <c r="P28" s="110"/>
+      <c r="Q28" s="110"/>
+      <c r="R28" s="110"/>
+      <c r="S28" s="93"/>
+      <c r="T28" s="92"/>
+      <c r="U28" s="93"/>
+      <c r="V28" s="92"/>
+      <c r="W28" s="110"/>
+      <c r="X28" s="93"/>
+      <c r="Y28" s="92"/>
+      <c r="Z28" s="93"/>
+      <c r="AA28" s="111"/>
+      <c r="AB28" s="111"/>
+      <c r="AC28" s="111"/>
       <c r="AD28" s="39"/>
-      <c r="AE28" s="104"/>
-      <c r="AF28" s="105"/>
-      <c r="AG28" s="106"/>
+      <c r="AE28" s="92"/>
+      <c r="AF28" s="110"/>
+      <c r="AG28" s="93"/>
       <c r="AH28" s="17"/>
       <c r="AI28" s="18"/>
       <c r="AJ28" s="3"/>
@@ -2513,44 +2577,44 @@
       <c r="AK30" s="56"/>
     </row>
     <row r="31" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="116" t="s">
+      <c r="A31" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="117"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="117"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="117"/>
-      <c r="P31" s="117"/>
-      <c r="Q31" s="117"/>
-      <c r="R31" s="117"/>
-      <c r="S31" s="117"/>
-      <c r="T31" s="117"/>
-      <c r="U31" s="117"/>
-      <c r="V31" s="117"/>
-      <c r="W31" s="117"/>
-      <c r="X31" s="117"/>
-      <c r="Y31" s="117"/>
-      <c r="Z31" s="117"/>
-      <c r="AA31" s="117"/>
-      <c r="AB31" s="118"/>
+      <c r="B31" s="121"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="121"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="121"/>
+      <c r="H31" s="121"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="121"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="121"/>
+      <c r="R31" s="121"/>
+      <c r="S31" s="121"/>
+      <c r="T31" s="121"/>
+      <c r="U31" s="121"/>
+      <c r="V31" s="121"/>
+      <c r="W31" s="121"/>
+      <c r="X31" s="121"/>
+      <c r="Y31" s="121"/>
+      <c r="Z31" s="121"/>
+      <c r="AA31" s="121"/>
+      <c r="AB31" s="122"/>
       <c r="AC31" s="57"/>
       <c r="AD31" s="57"/>
       <c r="AE31" s="57"/>
       <c r="AF31" s="57"/>
-      <c r="AG31" s="119"/>
-      <c r="AH31" s="119"/>
-      <c r="AI31" s="119"/>
-      <c r="AJ31" s="119"/>
+      <c r="AG31" s="123"/>
+      <c r="AH31" s="123"/>
+      <c r="AI31" s="123"/>
+      <c r="AJ31" s="123"/>
       <c r="AK31" s="58"/>
     </row>
   </sheetData>
@@ -2595,11 +2659,6 @@
     <mergeCell ref="O11:P11"/>
     <mergeCell ref="V11:W11"/>
     <mergeCell ref="AB11:AC11"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="AA15:AC15"/>
     <mergeCell ref="A29:AJ29"/>
     <mergeCell ref="A31:AB31"/>
     <mergeCell ref="AG31:AJ31"/>
@@ -2632,6 +2691,11 @@
     <mergeCell ref="M16:S16"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="V12:Z12"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="Y15:Z15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="AA15:AC15"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -2654,5 +2718,6 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="36" max="1048575" man="1"/>
   </colBreaks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>